--- a/docs/密度阶跃实验-实施方案与记录表.xlsx
+++ b/docs/密度阶跃实验-实施方案与记录表.xlsx
@@ -10,9 +10,10 @@
     <sheet name="实验概述" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="前置条件与安全" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="实验方案" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="采样记录表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="K计算表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="系统录入指引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="工况点登记表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="采样记录表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="K计算表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="系统录入指引" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -594,6 +595,21 @@
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>标准方案 6 阶段 × 2h = 12h(一个班次);最少可行方案 4 阶段(见实验方案 Sheet)。每阶段需要:密度调节 1 次、密度计/502灰分仪每 15min 抄表(各 8 点)、315 灰分化验 1~2 次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>工况记录(2026-09 补充)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>每轮实验必须登记工况标签(见「工况点登记表」):工作面/原煤灰分/带煤量/脱粉配置/系统组合/精磁尾液位(煤泥代理)/磁铁矿补加与分流(介质状态)/315与502平行样偏差;条件允许时每轮做一次原煤浮沉(可选性)试验。轮内保持稳定、轮间刻意反差——K 结果按工况标签归档,才能回答「K 是否随工况变化」并支撑分档(Stage 2)。</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1128,268 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>轮次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>日期/班次</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>工况点定位</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>工作面</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>原煤灰分(%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>带煤量均值(t/h)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>脱粉配置(473/474)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>系统组合</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>精磁尾液位均值(%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>磁铁矿补加(kg/h)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>分流量/喷水状态</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>原煤浮沉试验(有/无)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>315与502平行样偏差(%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>示例:第1轮</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 白班</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>高煤量×高灰分</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>44.1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>双开</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>A+B+401</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>有(λ曲线见化验台账)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>参考示例,正式行自行填写</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>第1轮</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr"/>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>第2轮</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>第4轮</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>登记规则:①每轮实验一行,K 结果按轮次贴工况标签(见 K计算表);②工况点定位从 2×2 网格选:煤量(&lt;800/≥800 t/h)×原煤灰分(&lt;40/≥40%),四轮覆盖四个象限;③轮内这些量必须稳定(见前置条件),轮间刻意反差——K 的工况差异才有信息量;④精磁尾液位是煤泥/介质状态的现成代理;磁铁矿补加量、分流量、喷水状态为介质系统操作量,每阶段在采样记录表备注中确认;⑤原煤浮沉试验可选但强烈推荐:λ曲线在分选密度附近的斜率就是「分选密度→精煤灰分」这段增益的机理值。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1124,8 +1401,12 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1176,12 +1457,32 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>精磁尾液位(%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>脱粉473</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>脱粉474</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>工作面</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>操作员</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>备注(扰动/介质操作)</t>
         </is>
       </c>
     </row>
@@ -1205,6 +1506,10 @@
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1226,6 +1531,10 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1247,6 +1556,10 @@
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1268,6 +1581,10 @@
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1289,6 +1606,10 @@
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1310,6 +1631,10 @@
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1331,6 +1656,10 @@
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1352,6 +1681,10 @@
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1373,6 +1706,10 @@
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1394,6 +1731,10 @@
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1415,6 +1756,10 @@
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1436,6 +1781,10 @@
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1457,6 +1806,10 @@
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1478,6 +1831,10 @@
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1499,6 +1856,10 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1520,6 +1881,10 @@
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1541,6 +1906,10 @@
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1562,6 +1931,10 @@
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1583,6 +1956,10 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1604,6 +1981,10 @@
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1625,6 +2006,10 @@
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1646,6 +2031,10 @@
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1667,6 +2056,10 @@
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1688,6 +2081,10 @@
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1709,6 +2106,10 @@
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1730,6 +2131,10 @@
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1751,6 +2156,10 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1772,6 +2181,10 @@
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1793,6 +2206,10 @@
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1814,6 +2231,10 @@
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1835,6 +2256,10 @@
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1856,6 +2281,10 @@
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1877,6 +2306,10 @@
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1898,6 +2331,10 @@
       <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1919,6 +2356,10 @@
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1940,6 +2381,10 @@
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1961,6 +2406,10 @@
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1982,6 +2431,10 @@
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2003,6 +2456,10 @@
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2024,6 +2481,10 @@
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2045,6 +2506,10 @@
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2066,6 +2531,10 @@
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2087,6 +2556,10 @@
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2108,6 +2581,10 @@
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2129,6 +2606,10 @@
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2150,6 +2631,10 @@
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2171,6 +2656,10 @@
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2192,11 +2681,15 @@
       <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>填写说明:①每行=一次抄表(建议15min间隔);②315化验有结果时填第6列,该行其余列照常抄;③密度计实测填调节到位后的稳定读数;④备注记录异常(停机/倒系统/加药变动)。</t>
+          <t>填写说明:①每行=一次抄表(建议15min间隔);②315化验有结果时填第6列,该行其余列照常抄;③密度计实测填调节到位后的稳定读数;④精磁尾液位=煤泥/介质状态代理,每行必抄;⑤脱粉/工作面逐行确认(变更即备注);⑥备注记录扰动(停机/倒系统/加药/带煤量波动&gt;±10%)与介质操作(磁铁矿补加/分流/喷水)——有扰动该阶段数据作废。</t>
         </is>
       </c>
     </row>
@@ -2205,13 +2698,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2245,12 +2738,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ρ0 基线密度</t>
+          <t>轮次/工况标签</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>P1 稳态密度计均值(g/cm³)</t>
+          <t>从「工况点登记表」抄:轮次+工况点定位+工作面(如 第1轮/高煤量×高灰分/3309)</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr"/>
@@ -2261,12 +2754,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>A0 基线灰分</t>
+          <t>ρ0 基线密度</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>P1 稳态 502 仪均值(%)</t>
+          <t>P1 稳态密度计均值(g/cm³)</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr"/>
@@ -2275,29 +2768,25 @@
       <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A0 基线灰分</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>P1 稳态 502 仪均值(%)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>#表头</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Δρ(稳态密度−ρ0)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ΔA(稳态502均值−A0)</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -2305,15 +2794,19 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>P2 (ρ0+0.01) 稳态密度</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>填 P2 判稳后密度均值</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
+          <t>#表头</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Δρ(稳态密度−ρ0)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ΔA(稳态502均值−A0)</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -2321,12 +2814,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>P2 稳态502灰分</t>
+          <t>P2 (ρ0+0.01) 稳态密度</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>填 P2 判稳后 502 均值(%)</t>
+          <t>填 P2 判稳后密度均值</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
@@ -2337,12 +2830,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>P3 回基线 稳态密度</t>
+          <t>P2 稳态502灰分</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>填 P3 判稳后密度均值</t>
+          <t>填 P2 判稳后 502 均值(%)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
@@ -2353,12 +2846,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>P3 稳态502灰分</t>
+          <t>P3 回基线 稳态密度</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>填 P3 判稳后 502 均值(%)</t>
+          <t>填 P3 判稳后密度均值</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
@@ -2369,12 +2862,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>P4 (ρ0−0.01) 稳态密度</t>
+          <t>P3 稳态502灰分</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>填 P4 判稳后密度均值</t>
+          <t>填 P3 判稳后 502 均值(%)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
@@ -2385,12 +2878,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>P4 稳态502灰分</t>
+          <t>P4 (ρ0−0.01) 稳态密度</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>填 P4 判稳后 502 均值(%)</t>
+          <t>填 P4 判稳后密度均值</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
@@ -2401,12 +2894,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>P6 (可选) 稳态密度</t>
+          <t>P4 稳态502灰分</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>填 P6 判稳后密度均值(未做留空)</t>
+          <t>填 P4 判稳后 502 均值(%)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr"/>
@@ -2417,12 +2910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>P6 稳态502灰分</t>
+          <t>P6 (可选) 稳态密度</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>填 P6 判稳后 502 均值(未做留空)</t>
+          <t>填 P6 判稳后密度均值(未做留空)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr"/>
@@ -2433,15 +2926,15 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>自动计算区</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>公式自动计算,无需填写</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
+          <t>P6 稳态502灰分</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>填 P6 判稳后 502 均值(未做留空)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -2455,60 +2948,49 @@
       <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>自动计算区</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>公式自动计算,无需填写</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>P2 ↑</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>IF(B6="","",B6-$B$2)</f>
-        <v/>
-      </c>
-      <c r="C17" s="7">
+      <c r="B18" s="7">
         <f>IF(B7="","",B7-$B$3)</f>
         <v/>
       </c>
-      <c r="D17" s="7">
-        <f>IF(OR(B6="",B7=""),"",(B6-$B$2)/(B7-$B$3))</f>
+      <c r="C18" s="7">
+        <f>IF(B8="","",B8-$B$4)</f>
         <v/>
       </c>
-      <c r="E17" s="7">
-        <f>IF(D17="","",IF((B6-$B$2)*(B7-$B$3)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
+      <c r="D18" s="7">
+        <f>IF(OR(B7="",B8=""),"",(B7-$B$3)/(B8-$B$4))</f>
         <v/>
       </c>
-      <c r="F17" s="7">
-        <f>IF(D17="","",IF(AND(D17&gt;0.005,D17&lt;0.2),"有效","越界(0.005~0.2),弃用"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>P3 ↓(回基线)</t>
-        </is>
-      </c>
-      <c r="B18" s="7">
-        <f>IF(B8="","",B8-$B$2)</f>
-        <v/>
-      </c>
-      <c r="C18" s="7">
-        <f>IF(B9="","",B9-$B$3)</f>
-        <v/>
-      </c>
-      <c r="D18" s="7">
-        <f>IF(OR(B8="",B9=""),"",(B8-$B$2)/(B9-$B$3))</f>
-        <v/>
-      </c>
       <c r="E18" s="7">
-        <f>IF(D18="","",IF((B8-$B$2)*(B9-$B$3)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
+        <f>IF(D18="","",IF((B7-$B$3)*(B8-$B$4)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
         <v/>
       </c>
       <c r="F18" s="7">
@@ -2519,23 +3001,23 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>P4 ↓</t>
+          <t>P3 ↓(回基线)</t>
         </is>
       </c>
       <c r="B19" s="7">
-        <f>IF(B10="","",B10-$B$2)</f>
+        <f>IF(B9="","",B9-$B$3)</f>
         <v/>
       </c>
       <c r="C19" s="7">
-        <f>IF(B11="","",B11-$B$3)</f>
+        <f>IF(B10="","",B10-$B$4)</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IF(OR(B10="",B11=""),"",(B10-$B$2)/(B11-$B$3))</f>
+        <f>IF(OR(B9="",B10=""),"",(B9-$B$3)/(B10-$B$4))</f>
         <v/>
       </c>
       <c r="E19" s="7">
-        <f>IF(D19="","",IF((B10-$B$2)*(B11-$B$3)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
+        <f>IF(D19="","",IF((B9-$B$3)*(B10-$B$4)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
         <v/>
       </c>
       <c r="F19" s="7">
@@ -2546,23 +3028,23 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>P6(可选)</t>
+          <t>P4 ↓</t>
         </is>
       </c>
       <c r="B20" s="7">
-        <f>IF(B12="","",B12-$B$2)</f>
+        <f>IF(B11="","",B11-$B$3)</f>
         <v/>
       </c>
       <c r="C20" s="7">
-        <f>IF(B13="","",B13-$B$3)</f>
+        <f>IF(B12="","",B12-$B$4)</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IF(OR(B12="",B13=""),"",(B12-$B$2)/(B13-$B$3))</f>
+        <f>IF(OR(B11="",B12=""),"",(B11-$B$3)/(B12-$B$4))</f>
         <v/>
       </c>
       <c r="E20" s="7">
-        <f>IF(D20="","",IF((B12-$B$2)*(B13-$B$3)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
+        <f>IF(D20="","",IF((B11-$B$3)*(B12-$B$4)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
         <v/>
       </c>
       <c r="F20" s="7">
@@ -2573,26 +3055,38 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>K 平均值</t>
+          <t>P6(可选)</t>
         </is>
       </c>
       <c r="B21" s="7">
-        <f>IFERROR(AVERAGE(D17:D20),"")</f>
+        <f>IF(B13="","",B13-$B$3)</f>
         <v/>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="C21" s="7">
+        <f>IF(B14="","",B14-$B$4)</f>
+        <v/>
+      </c>
+      <c r="D21" s="7">
+        <f>IF(OR(B13="",B14=""),"",(B13-$B$3)/(B14-$B$4))</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
+        <f>IF(D21="","",IF((B13-$B$3)*(B14-$B$4)&gt;0,"同向(密度↑灰分↑)","反向!检查数据"))</f>
+        <v/>
+      </c>
+      <c r="F21" s="7">
+        <f>IF(D21="","",IF(AND(D21&gt;0.005,D21&lt;0.2),"有效","越界(0.005~0.2),弃用"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>K 标准差</t>
+          <t>K 平均值</t>
         </is>
       </c>
       <c r="B22" s="7">
-        <f>IFERROR(STDEV(D17:D20),"")</f>
+        <f>IFERROR(AVERAGE(D18:D21),"")</f>
         <v/>
       </c>
       <c r="C22" s="7" t="n"/>
@@ -2603,18 +3097,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>变异系数CV</t>
+          <t>K 标准差</t>
         </is>
       </c>
       <c r="B23" s="7">
-        <f>IFERROR(B22/B21,"")</f>
+        <f>IFERROR(STDEV(D18:D21),"")</f>
         <v/>
       </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>CV&lt;30% 视为可辨识;≥30% 说明信号不足或工况漂移</t>
-        </is>
-      </c>
+      <c r="C23" s="7" t="n"/>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
       <c r="F23" s="7" t="n"/>
@@ -2622,16 +3112,16 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>与专家值对比</t>
+          <t>变异系数CV</t>
         </is>
       </c>
       <c r="B24" s="7">
-        <f>IF(B21="","",B21-0.075)</f>
+        <f>IFERROR(B23/B22,"")</f>
         <v/>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>与专家表反推值 0.075 的偏差;±0.02 内认为经验值得到验证</t>
+          <t>CV&lt;30% 视为可辨识;≥30% 说明信号不足或工况漂移</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
@@ -2641,30 +3131,69 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>结论建议</t>
+          <t>与专家值对比</t>
         </is>
       </c>
       <c r="B25" s="7">
-        <f>IF(B21="","待填",IF(ABS(B21-0.075)&lt;0.02,"专家值得到验证,维持现行专家表",IF(B23&gt;0.3,"信号不足:加做0.02步长(P6)或延长保持时间","建议按实测K修订专家表与K_PREDICT")))</f>
+        <f>IF(B22="","",B22-0.075)</f>
         <v/>
       </c>
-      <c r="C25" s="7" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>与专家表反推值 0.075 的偏差;±0.02 内认为经验值得到验证</t>
+        </is>
+      </c>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>结论建议</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>IF(B22="","待填",IF(ABS(B22-0.075)&lt;0.02,"专家值得到验证,维持现行专家表",IF(B24&gt;0.3,"信号不足:加做0.02步长(P6)或延长保持时间","建议按实测K修订专家表与K_PREDICT")))</f>
+        <v/>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>跨工况对比:每轮一张本表副本,按「工况点登记表」的轮次标签汇总各轮 K —— 轮间 K 差异 &gt; 各轮合并 CV 才值得分档(Stage 2 分档专家表的判据)。</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2815,6 +3344,26 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>与决策日志的协同</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>实验期间的密度调节若通过系统界面执行(在线仪表区改密度),Stage 0 决策日志会自动记录每次调整与当时的工况上下文(带煤量/原煤灰分/脱粉/工作面/液位),45分钟后自动补记灰分响应——Excel 为正式记录,决策日志为自动备份,两边可互相校验</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>查看:GET /api/v1/state → densityDecisionLog;密度也可事后按表3格式补录</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
